--- a/artfynd/A 20426-2023 artfynd.xlsx
+++ b/artfynd/A 20426-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5475488</v>
+        <v>137133484</v>
       </c>
       <c r="B2" t="n">
-        <v>101079</v>
+        <v>77865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222815</v>
+        <v>1342</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corydalis cava</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Schweigg. &amp; Körte</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Weigel) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Siesjö, NV. Vidriksberg, 700 m öster, Sk</t>
+          <t>Ryssbergets naturreservat, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471875</v>
+        <v>472022</v>
       </c>
       <c r="R2" t="n">
-        <v>6213776</v>
+        <v>6213887</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -752,24 +743,14 @@
           <t>Ivetofta</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>M-Brm-0181</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-05-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>500 röda ex. + 100 vita ex.</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,20 +765,141 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>David Göransson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>David Göransson, Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137133484</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5475488</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101079</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222815</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hålnunneört</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Corydalis cava</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Schweigg. &amp; Körte</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Siesjö, NV. Vidriksberg, 700 m öster, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>471875</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6213776</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bromölla</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ivetofta</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>M-Brm-0181</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2012-05-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2012-05-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>500 röda ex. + 100 vita ex.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Skåne Floraväktarna</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Sam Skällberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/5475488</t>
         </is>
@@ -806,6 +908,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20426-2023 artfynd.xlsx
+++ b/artfynd/A 20426-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137133484</v>
       </c>
       <c r="B2" t="n">
-        <v>77865</v>
+        <v>77867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20426-2023 artfynd.xlsx
+++ b/artfynd/A 20426-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137133484</v>
       </c>
       <c r="B2" t="n">
-        <v>77867</v>
+        <v>77880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20426-2023 artfynd.xlsx
+++ b/artfynd/A 20426-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137133484</v>
       </c>
       <c r="B2" t="n">
-        <v>77880</v>
+        <v>77882</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20426-2023 artfynd.xlsx
+++ b/artfynd/A 20426-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137133484</v>
       </c>
       <c r="B2" t="n">
-        <v>77882</v>
+        <v>77892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20426-2023 artfynd.xlsx
+++ b/artfynd/A 20426-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137133484</v>
       </c>
       <c r="B2" t="n">
-        <v>77892</v>
+        <v>77895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20426-2023 artfynd.xlsx
+++ b/artfynd/A 20426-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137133484</v>
       </c>
       <c r="B2" t="n">
-        <v>77895</v>
+        <v>77900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20426-2023 artfynd.xlsx
+++ b/artfynd/A 20426-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137133484</v>
       </c>
       <c r="B2" t="n">
-        <v>77900</v>
+        <v>77911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20426-2023 artfynd.xlsx
+++ b/artfynd/A 20426-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137133484</v>
       </c>
       <c r="B2" t="n">
-        <v>77911</v>
+        <v>77912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20426-2023 artfynd.xlsx
+++ b/artfynd/A 20426-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137133484</v>
       </c>
       <c r="B2" t="n">
-        <v>77912</v>
+        <v>77916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
